--- a/model_diagnostics_attachment.xlsx
+++ b/model_diagnostics_attachment.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Результаты" sheetId="1" r:id="Rdb11d55151c14f11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PSI признаков" sheetId="2" r:id="R12e4fcc3208e4522"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Методика" sheetId="3" r:id="R45eebd08d9b547ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Результаты" sheetId="1" r:id="R301e24bd34f34f04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PSI признаков" sheetId="2" r:id="R3986dca122ca4b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Связь с таргетом" sheetId="3" r:id="R399c4166068b4930"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Методика" sheetId="4" r:id="R8c8129e2644f4064"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -93,7 +94,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="47">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -210,6 +211,12 @@
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2834,6 +2841,1496 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="95" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="23" customHeight="1">
+      <x:c r="A1" s="2"/>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="1"/>
+      <x:c r="I1" s="1"/>
+      <x:c r="J1" s="1"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="2"/>
+      <x:c r="B2" s="3" t="str">
+        <x:v>Связь числовых признаков с таргетом</x:v>
+      </x:c>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+    </x:row>
+    <x:row r="3" ht="23" customHeight="1">
+      <x:c r="A3" s="2"/>
+      <x:c r="B3" s="4" t="str">
+        <x:v>Источник: предоставленные результаты monthly_feature_auc_wide. AUC перенесён со скриншотов с точностью 6 знаков.</x:v>
+      </x:c>
+      <x:c r="C3" s="2"/>
+      <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+    </x:row>
+    <x:row r="4" ht="23" customHeight="1">
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="4" t="str">
+        <x:v>Для каждого месяца: roc_auc_score(Y, X), где скор — значение одного признака, таргет — своего месяца. Обучения модели нет.</x:v>
+      </x:c>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="23" customHeight="1">
+      <x:c r="A5" s="2"/>
+      <x:c r="B5" s="4" t="str">
+        <x:v>Все контракты месяца с конечным заполненным значением признака. Состав строк может различаться по месяцам и признакам.</x:v>
+      </x:c>
+      <x:c r="C5" s="2"/>
+      <x:c r="D5" s="2"/>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="1"/>
+      <x:c r="I5" s="1"/>
+      <x:c r="J5" s="1"/>
+    </x:row>
+    <x:row r="6" ht="23" customHeight="1">
+      <x:c r="A6" s="2"/>
+      <x:c r="B6" s="4" t="str">
+        <x:v>AUC &gt; 0,5 — прямая связь; AUC &lt; 0,5 — обратная. Около 0,5 — слабое монотонное ранжирование; нелинейная связь может сохраняться.</x:v>
+      </x:c>
+      <x:c r="C6" s="2"/>
+      <x:c r="D6" s="2"/>
+      <x:c r="E6" s="2"/>
+      <x:c r="F6" s="2"/>
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="1"/>
+      <x:c r="I6" s="1"/>
+      <x:c r="J6" s="1"/>
+    </x:row>
+    <x:row r="7" ht="23" customHeight="1">
+      <x:c r="A7" s="2"/>
+      <x:c r="B7" s="4" t="str">
+        <x:v>Изменение силы = |AUC позднего месяца − 0,5| − |AUC раннего месяца − 0,5|. Отрицательное значение означает ослабление.</x:v>
+      </x:c>
+      <x:c r="C7" s="2"/>
+      <x:c r="D7" s="2"/>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="1"/>
+      <x:c r="I7" s="1"/>
+      <x:c r="J7" s="1"/>
+    </x:row>
+    <x:row r="8" ht="23" customHeight="1">
+      <x:c r="A8" s="2"/>
+      <x:c r="B8" s="4" t="str">
+        <x:v>Однофакторный AUC не измеряет вклад признака в модель и не учитывает взаимодействия. Изменение направления видно по исходным AUC.</x:v>
+      </x:c>
+      <x:c r="C8" s="2"/>
+      <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="1"/>
+      <x:c r="I8" s="1"/>
+      <x:c r="J8" s="1"/>
+    </x:row>
+    <x:row r="9" ht="23" customHeight="1">
+      <x:c r="A9" s="2"/>
+      <x:c r="B9" s="2"/>
+      <x:c r="C9" s="2"/>
+      <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="1"/>
+      <x:c r="I9" s="1"/>
+      <x:c r="J9" s="1"/>
+    </x:row>
+    <x:row r="10" ht="50" customHeight="1">
+      <x:c r="A10" s="2"/>
+      <x:c r="B10" s="10" t="str">
+        <x:v>Признак</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>2025-09</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="str">
+        <x:v>2025-10</x:v>
+      </x:c>
+      <x:c r="E10" s="10" t="str">
+        <x:v>2025-11</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="str">
+        <x:v>2025-12</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="str">
+        <x:v>2026-01</x:v>
+      </x:c>
+      <x:c r="H10" s="10" t="str">
+        <x:v>2026-02</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="str">
+        <x:v>Δ силы: февраль к сентябрю</x:v>
+      </x:c>
+      <x:c r="J10" s="10" t="str">
+        <x:v>Δ силы: февраль к январю</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="35" customHeight="1">
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="34" t="str">
+        <x:v>util_current</x:v>
+      </x:c>
+      <x:c r="C11" s="42" t="n">
+        <x:v>0.707501</x:v>
+      </x:c>
+      <x:c r="D11" s="42" t="n">
+        <x:v>0.713803</x:v>
+      </x:c>
+      <x:c r="E11" s="42" t="n">
+        <x:v>0.725805</x:v>
+      </x:c>
+      <x:c r="F11" s="42" t="n">
+        <x:v>0.744542</x:v>
+      </x:c>
+      <x:c r="G11" s="42" t="n">
+        <x:v>0.741752</x:v>
+      </x:c>
+      <x:c r="H11" s="42" t="n">
+        <x:v>0.729616</x:v>
+      </x:c>
+      <x:c r="I11" s="42" t="n">
+        <x:f>ABS(H11-0.5)-ABS(C11-0.5)</x:f>
+        <x:v>0.022114999999999996</x:v>
+      </x:c>
+      <x:c r="J11" s="42" t="n">
+        <x:f>ABS(H11-0.5)-ABS(G11-0.5)</x:f>
+        <x:v>-0.012135999999999925</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="35" customHeight="1">
+      <x:c r="A12" s="2"/>
+      <x:c r="B12" s="37" t="str">
+        <x:v>contract_cred_contract_uid_by_status_nm_wrk_by_product_category_nm_ptb_cc_aggcnt</x:v>
+      </x:c>
+      <x:c r="C12" s="43" t="n">
+        <x:v>0.756622</x:v>
+      </x:c>
+      <x:c r="D12" s="43" t="n">
+        <x:v>0.724054</x:v>
+      </x:c>
+      <x:c r="E12" s="43" t="n">
+        <x:v>0.69032</x:v>
+      </x:c>
+      <x:c r="F12" s="43" t="n">
+        <x:v>0.66531</x:v>
+      </x:c>
+      <x:c r="G12" s="43" t="n">
+        <x:v>0.64728</x:v>
+      </x:c>
+      <x:c r="H12" s="43" t="n">
+        <x:v>0.626619</x:v>
+      </x:c>
+      <x:c r="I12" s="42" t="n">
+        <x:f>ABS(H12-0.5)-ABS(C12-0.5)</x:f>
+        <x:v>-0.13000299999999998</x:v>
+      </x:c>
+      <x:c r="J12" s="42" t="n">
+        <x:f>ABS(H12-0.5)-ABS(G12-0.5)</x:f>
+        <x:v>-0.02066099999999993</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="35" customHeight="1">
+      <x:c r="A13" s="2"/>
+      <x:c r="B13" s="34" t="str">
+        <x:v>util_daily_max_180d</x:v>
+      </x:c>
+      <x:c r="C13" s="42" t="n">
+        <x:v>0.702262</x:v>
+      </x:c>
+      <x:c r="D13" s="42" t="n">
+        <x:v>0.708511</x:v>
+      </x:c>
+      <x:c r="E13" s="42" t="n">
+        <x:v>0.717475</x:v>
+      </x:c>
+      <x:c r="F13" s="42" t="n">
+        <x:v>0.735528</x:v>
+      </x:c>
+      <x:c r="G13" s="42" t="n">
+        <x:v>0.732029</x:v>
+      </x:c>
+      <x:c r="H13" s="42" t="n">
+        <x:v>0.720523</x:v>
+      </x:c>
+      <x:c r="I13" s="42" t="n">
+        <x:f>ABS(H13-0.5)-ABS(C13-0.5)</x:f>
+        <x:v>0.01826099999999997</x:v>
+      </x:c>
+      <x:c r="J13" s="42" t="n">
+        <x:f>ABS(H13-0.5)-ABS(G13-0.5)</x:f>
+        <x:v>-0.011506000000000016</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="35" customHeight="1">
+      <x:c r="A14" s="2"/>
+      <x:c r="B14" s="37" t="str">
+        <x:v>contract_cred_current_debt_amt_by_status_nm_wrk_by_product_category_nm_ptb_cc_aggsum</x:v>
+      </x:c>
+      <x:c r="C14" s="43" t="n">
+        <x:v>0.75307</x:v>
+      </x:c>
+      <x:c r="D14" s="43" t="n">
+        <x:v>0.717053</x:v>
+      </x:c>
+      <x:c r="E14" s="43" t="n">
+        <x:v>0.685905</x:v>
+      </x:c>
+      <x:c r="F14" s="43" t="n">
+        <x:v>0.667252</x:v>
+      </x:c>
+      <x:c r="G14" s="43" t="n">
+        <x:v>0.654881</x:v>
+      </x:c>
+      <x:c r="H14" s="43" t="n">
+        <x:v>0.640164</x:v>
+      </x:c>
+      <x:c r="I14" s="42" t="n">
+        <x:f>ABS(H14-0.5)-ABS(C14-0.5)</x:f>
+        <x:v>-0.11290600000000006</x:v>
+      </x:c>
+      <x:c r="J14" s="42" t="n">
+        <x:f>ABS(H14-0.5)-ABS(G14-0.5)</x:f>
+        <x:v>-0.014717000000000091</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="35" customHeight="1">
+      <x:c r="A15" s="2"/>
+      <x:c r="B15" s="34" t="str">
+        <x:v>contract_cred_current_debt_amt_by_status_nm_wrk_by_product_category_nm_ptb_cc_aggmin</x:v>
+      </x:c>
+      <x:c r="C15" s="42" t="n">
+        <x:v>0.642044</x:v>
+      </x:c>
+      <x:c r="D15" s="42" t="n">
+        <x:v>0.634212</x:v>
+      </x:c>
+      <x:c r="E15" s="42" t="n">
+        <x:v>0.63368</x:v>
+      </x:c>
+      <x:c r="F15" s="42" t="n">
+        <x:v>0.628502</x:v>
+      </x:c>
+      <x:c r="G15" s="42" t="n">
+        <x:v>0.615411</x:v>
+      </x:c>
+      <x:c r="H15" s="42" t="n">
+        <x:v>0.602808</x:v>
+      </x:c>
+      <x:c r="I15" s="42" t="n">
+        <x:f>ABS(H15-0.5)-ABS(C15-0.5)</x:f>
+        <x:v>-0.03923599999999994</x:v>
+      </x:c>
+      <x:c r="J15" s="42" t="n">
+        <x:f>ABS(H15-0.5)-ABS(G15-0.5)</x:f>
+        <x:v>-0.01260300000000003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="35" customHeight="1">
+      <x:c r="A16" s="2"/>
+      <x:c r="B16" s="37" t="str">
+        <x:v>current_limit</x:v>
+      </x:c>
+      <x:c r="C16" s="43" t="n">
+        <x:v>0.433404</x:v>
+      </x:c>
+      <x:c r="D16" s="43" t="n">
+        <x:v>0.421952</x:v>
+      </x:c>
+      <x:c r="E16" s="43" t="n">
+        <x:v>0.41589</x:v>
+      </x:c>
+      <x:c r="F16" s="43" t="n">
+        <x:v>0.404188</x:v>
+      </x:c>
+      <x:c r="G16" s="43" t="n">
+        <x:v>0.403703</x:v>
+      </x:c>
+      <x:c r="H16" s="43" t="n">
+        <x:v>0.404396</x:v>
+      </x:c>
+      <x:c r="I16" s="42" t="n">
+        <x:f>ABS(H16-0.5)-ABS(C16-0.5)</x:f>
+        <x:v>0.029008000000000034</x:v>
+      </x:c>
+      <x:c r="J16" s="42" t="n">
+        <x:f>ABS(H16-0.5)-ABS(G16-0.5)</x:f>
+        <x:v>-0.0006929999999999992</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="35" customHeight="1">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="34" t="str">
+        <x:v>contract_cred_current_debt_amt_by_status_nm_wrk_by_product_category_nm_ptb_cc_aggmax</x:v>
+      </x:c>
+      <x:c r="C17" s="42" t="n">
+        <x:v>0.615282</x:v>
+      </x:c>
+      <x:c r="D17" s="42" t="n">
+        <x:v>0.600039</x:v>
+      </x:c>
+      <x:c r="E17" s="42" t="n">
+        <x:v>0.59502</x:v>
+      </x:c>
+      <x:c r="F17" s="42" t="n">
+        <x:v>0.582896</x:v>
+      </x:c>
+      <x:c r="G17" s="42" t="n">
+        <x:v>0.578748</x:v>
+      </x:c>
+      <x:c r="H17" s="42" t="n">
+        <x:v>0.572785</x:v>
+      </x:c>
+      <x:c r="I17" s="42" t="n">
+        <x:f>ABS(H17-0.5)-ABS(C17-0.5)</x:f>
+        <x:v>-0.04249700000000001</x:v>
+      </x:c>
+      <x:c r="J17" s="42" t="n">
+        <x:f>ABS(H17-0.5)-ABS(G17-0.5)</x:f>
+        <x:v>-0.005963000000000052</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="35" customHeight="1">
+      <x:c r="A18" s="2"/>
+      <x:c r="B18" s="37" t="str">
+        <x:v>contract_dep_contract_uid_by_status_nm_wrk_by_product_category_nm_dc_curr_acc_aggcnt</x:v>
+      </x:c>
+      <x:c r="C18" s="43" t="n">
+        <x:v>0.730525</x:v>
+      </x:c>
+      <x:c r="D18" s="43" t="n">
+        <x:v>0.699114</x:v>
+      </x:c>
+      <x:c r="E18" s="43" t="n">
+        <x:v>0.664704</x:v>
+      </x:c>
+      <x:c r="F18" s="43" t="n">
+        <x:v>0.640993</x:v>
+      </x:c>
+      <x:c r="G18" s="43" t="n">
+        <x:v>0.626038</x:v>
+      </x:c>
+      <x:c r="H18" s="43" t="n">
+        <x:v>0.609096</x:v>
+      </x:c>
+      <x:c r="I18" s="42" t="n">
+        <x:f>ABS(H18-0.5)-ABS(C18-0.5)</x:f>
+        <x:v>-0.12142900000000001</x:v>
+      </x:c>
+      <x:c r="J18" s="42" t="n">
+        <x:f>ABS(H18-0.5)-ABS(G18-0.5)</x:f>
+        <x:v>-0.016942000000000013</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="35" customHeight="1">
+      <x:c r="A19" s="2"/>
+      <x:c r="B19" s="34" t="str">
+        <x:v>crds_cci_agreewithpresale_aggsum_d90</x:v>
+      </x:c>
+      <x:c r="C19" s="42" t="n">
+        <x:v>0.474287</x:v>
+      </x:c>
+      <x:c r="D19" s="42" t="n">
+        <x:v>0.470572</x:v>
+      </x:c>
+      <x:c r="E19" s="42" t="n">
+        <x:v>0.470784</x:v>
+      </x:c>
+      <x:c r="F19" s="42" t="n">
+        <x:v>0.46984</x:v>
+      </x:c>
+      <x:c r="G19" s="42" t="n">
+        <x:v>0.471796</x:v>
+      </x:c>
+      <x:c r="H19" s="42" t="n">
+        <x:v>0.479281</x:v>
+      </x:c>
+      <x:c r="I19" s="42" t="n">
+        <x:f>ABS(H19-0.5)-ABS(C19-0.5)</x:f>
+        <x:v>-0.0049939999999999984</x:v>
+      </x:c>
+      <x:c r="J19" s="42" t="n">
+        <x:f>ABS(H19-0.5)-ABS(G19-0.5)</x:f>
+        <x:v>-0.007485000000000019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="35" customHeight="1">
+      <x:c r="A20" s="2"/>
+      <x:c r="B20" s="37" t="str">
+        <x:v>contract_agg_monthly_cred_cntr_current_interest_rate_1m</x:v>
+      </x:c>
+      <x:c r="C20" s="43" t="n">
+        <x:v>0.487237</x:v>
+      </x:c>
+      <x:c r="D20" s="43" t="n">
+        <x:v>0.489072</x:v>
+      </x:c>
+      <x:c r="E20" s="43" t="n">
+        <x:v>0.493584</x:v>
+      </x:c>
+      <x:c r="F20" s="43" t="n">
+        <x:v>0.498818</x:v>
+      </x:c>
+      <x:c r="G20" s="43" t="n">
+        <x:v>0.500874</x:v>
+      </x:c>
+      <x:c r="H20" s="43" t="n">
+        <x:v>0.501368</x:v>
+      </x:c>
+      <x:c r="I20" s="42" t="n">
+        <x:f>ABS(H20-0.5)-ABS(C20-0.5)</x:f>
+        <x:v>-0.011394999999999988</x:v>
+      </x:c>
+      <x:c r="J20" s="42" t="n">
+        <x:f>ABS(H20-0.5)-ABS(G20-0.5)</x:f>
+        <x:v>0.0004939999999999944</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="35" customHeight="1">
+      <x:c r="A21" s="2"/>
+      <x:c r="B21" s="34" t="str">
+        <x:v>contract_cred_current_debt_amt_by_status_nm_wrk_by_product_category_nm_ptb_cc_aggavg</x:v>
+      </x:c>
+      <x:c r="C21" s="42" t="n">
+        <x:v>0.638196</x:v>
+      </x:c>
+      <x:c r="D21" s="42" t="n">
+        <x:v>0.623794</x:v>
+      </x:c>
+      <x:c r="E21" s="42" t="n">
+        <x:v>0.616388</x:v>
+      </x:c>
+      <x:c r="F21" s="42" t="n">
+        <x:v>0.609366</x:v>
+      </x:c>
+      <x:c r="G21" s="42" t="n">
+        <x:v>0.602528</x:v>
+      </x:c>
+      <x:c r="H21" s="42" t="n">
+        <x:v>0.593942</x:v>
+      </x:c>
+      <x:c r="I21" s="42" t="n">
+        <x:f>ABS(H21-0.5)-ABS(C21-0.5)</x:f>
+        <x:v>-0.044254000000000016</x:v>
+      </x:c>
+      <x:c r="J21" s="42" t="n">
+        <x:f>ABS(H21-0.5)-ABS(G21-0.5)</x:f>
+        <x:v>-0.008585999999999983</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="35" customHeight="1">
+      <x:c r="A22" s="2"/>
+      <x:c r="B22" s="37" t="str">
+        <x:v>contract_cred_contract_uid_by_product_category_nm_ptb_cc_aggcnt_d730</x:v>
+      </x:c>
+      <x:c r="C22" s="43" t="n">
+        <x:v>0.665431</x:v>
+      </x:c>
+      <x:c r="D22" s="43" t="n">
+        <x:v>0.636656</x:v>
+      </x:c>
+      <x:c r="E22" s="43" t="n">
+        <x:v>0.607895</x:v>
+      </x:c>
+      <x:c r="F22" s="43" t="n">
+        <x:v>0.587871</x:v>
+      </x:c>
+      <x:c r="G22" s="43" t="n">
+        <x:v>0.575239</x:v>
+      </x:c>
+      <x:c r="H22" s="43" t="n">
+        <x:v>0.559675</x:v>
+      </x:c>
+      <x:c r="I22" s="42" t="n">
+        <x:f>ABS(H22-0.5)-ABS(C22-0.5)</x:f>
+        <x:v>-0.10575599999999996</x:v>
+      </x:c>
+      <x:c r="J22" s="42" t="n">
+        <x:f>ABS(H22-0.5)-ABS(G22-0.5)</x:f>
+        <x:v>-0.015563999999999911</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="35" customHeight="1">
+      <x:c r="A23" s="2"/>
+      <x:c r="B23" s="34" t="str">
+        <x:v>crds_cci_max_limit_presale_div_max_limit_tariff_aggmax_d90</x:v>
+      </x:c>
+      <x:c r="C23" s="42" t="n">
+        <x:v>0.484402</x:v>
+      </x:c>
+      <x:c r="D23" s="42" t="n">
+        <x:v>0.480125</x:v>
+      </x:c>
+      <x:c r="E23" s="42" t="n">
+        <x:v>0.48094</x:v>
+      </x:c>
+      <x:c r="F23" s="42" t="n">
+        <x:v>0.480885</x:v>
+      </x:c>
+      <x:c r="G23" s="42" t="n">
+        <x:v>0.48058</x:v>
+      </x:c>
+      <x:c r="H23" s="42" t="n">
+        <x:v>0.48449</x:v>
+      </x:c>
+      <x:c r="I23" s="42" t="n">
+        <x:f>ABS(H23-0.5)-ABS(C23-0.5)</x:f>
+        <x:v>-0.00008799999999997699</x:v>
+      </x:c>
+      <x:c r="J23" s="42" t="n">
+        <x:f>ABS(H23-0.5)-ABS(G23-0.5)</x:f>
+        <x:v>-0.003909999999999969</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="35" customHeight="1">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="37" t="str">
+        <x:v>contract_cred_contract_amt_by_status_nm_wrk_by_product_category_nm_ptb_cc_aggmax</x:v>
+      </x:c>
+      <x:c r="C24" s="43" t="n">
+        <x:v>0.434118</x:v>
+      </x:c>
+      <x:c r="D24" s="43" t="n">
+        <x:v>0.421654</x:v>
+      </x:c>
+      <x:c r="E24" s="43" t="n">
+        <x:v>0.415294</x:v>
+      </x:c>
+      <x:c r="F24" s="43" t="n">
+        <x:v>0.404159</x:v>
+      </x:c>
+      <x:c r="G24" s="43" t="n">
+        <x:v>0.405342</x:v>
+      </x:c>
+      <x:c r="H24" s="43" t="n">
+        <x:v>0.406858</x:v>
+      </x:c>
+      <x:c r="I24" s="42" t="n">
+        <x:f>ABS(H24-0.5)-ABS(C24-0.5)</x:f>
+        <x:v>0.027260000000000006</x:v>
+      </x:c>
+      <x:c r="J24" s="42" t="n">
+        <x:f>ABS(H24-0.5)-ABS(G24-0.5)</x:f>
+        <x:v>-0.0015160000000000173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="35" customHeight="1">
+      <x:c r="A25" s="2"/>
+      <x:c r="B25" s="34" t="str">
+        <x:v>application_approved_product_by_cardcred_report_dt_diff_open_dt_aggmin</x:v>
+      </x:c>
+      <x:c r="C25" s="42" t="n">
+        <x:v>0.576126</x:v>
+      </x:c>
+      <x:c r="D25" s="42" t="n">
+        <x:v>0.582663</x:v>
+      </x:c>
+      <x:c r="E25" s="42" t="n">
+        <x:v>0.584975</x:v>
+      </x:c>
+      <x:c r="F25" s="42" t="n">
+        <x:v>0.592936</x:v>
+      </x:c>
+      <x:c r="G25" s="42" t="n">
+        <x:v>0.589395</x:v>
+      </x:c>
+      <x:c r="H25" s="42" t="n">
+        <x:v>0.585439</x:v>
+      </x:c>
+      <x:c r="I25" s="42" t="n">
+        <x:f>ABS(H25-0.5)-ABS(C25-0.5)</x:f>
+        <x:v>0.009313000000000016</x:v>
+      </x:c>
+      <x:c r="J25" s="42" t="n">
+        <x:f>ABS(H25-0.5)-ABS(G25-0.5)</x:f>
+        <x:v>-0.0039559999999999595</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="35" customHeight="1">
+      <x:c r="A26" s="2"/>
+      <x:c r="B26" s="37" t="str">
+        <x:v>contract_cred_current_debt_amt_by_status_nm_wrk_aggmin</x:v>
+      </x:c>
+      <x:c r="C26" s="43" t="n">
+        <x:v>0.638826</x:v>
+      </x:c>
+      <x:c r="D26" s="43" t="n">
+        <x:v>0.631991</x:v>
+      </x:c>
+      <x:c r="E26" s="43" t="n">
+        <x:v>0.632431</x:v>
+      </x:c>
+      <x:c r="F26" s="43" t="n">
+        <x:v>0.627874</x:v>
+      </x:c>
+      <x:c r="G26" s="43" t="n">
+        <x:v>0.6147</x:v>
+      </x:c>
+      <x:c r="H26" s="43" t="n">
+        <x:v>0.601964</x:v>
+      </x:c>
+      <x:c r="I26" s="42" t="n">
+        <x:f>ABS(H26-0.5)-ABS(C26-0.5)</x:f>
+        <x:v>-0.03686199999999995</x:v>
+      </x:c>
+      <x:c r="J26" s="42" t="n">
+        <x:f>ABS(H26-0.5)-ABS(G26-0.5)</x:f>
+        <x:v>-0.01273599999999997</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="35" customHeight="1">
+      <x:c r="A27" s="2"/>
+      <x:c r="B27" s="34" t="str">
+        <x:v>contract_agg_monthly_cred_cntr_paid_principal_sum_cnt_months_pos_3m</x:v>
+      </x:c>
+      <x:c r="C27" s="42" t="n">
+        <x:v>0.56382</x:v>
+      </x:c>
+      <x:c r="D27" s="42" t="n">
+        <x:v>0.559851</x:v>
+      </x:c>
+      <x:c r="E27" s="42" t="n">
+        <x:v>0.549345</x:v>
+      </x:c>
+      <x:c r="F27" s="42" t="n">
+        <x:v>0.539427</x:v>
+      </x:c>
+      <x:c r="G27" s="42" t="n">
+        <x:v>0.545189</x:v>
+      </x:c>
+      <x:c r="H27" s="42" t="n">
+        <x:v>0.541992</x:v>
+      </x:c>
+      <x:c r="I27" s="42" t="n">
+        <x:f>ABS(H27-0.5)-ABS(C27-0.5)</x:f>
+        <x:v>-0.02182799999999996</x:v>
+      </x:c>
+      <x:c r="J27" s="42" t="n">
+        <x:f>ABS(H27-0.5)-ABS(G27-0.5)</x:f>
+        <x:v>-0.0031970000000000054</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="35" customHeight="1">
+      <x:c r="A28" s="2"/>
+      <x:c r="B28" s="37" t="str">
+        <x:v>contract_cred_contract_uid_by_status_nm_wrk_div_contract_uid_aggcnt</x:v>
+      </x:c>
+      <x:c r="C28" s="43" t="n">
+        <x:v>0.557946</x:v>
+      </x:c>
+      <x:c r="D28" s="43" t="n">
+        <x:v>0.557482</x:v>
+      </x:c>
+      <x:c r="E28" s="43" t="n">
+        <x:v>0.557888</x:v>
+      </x:c>
+      <x:c r="F28" s="43" t="n">
+        <x:v>0.556949</x:v>
+      </x:c>
+      <x:c r="G28" s="43" t="n">
+        <x:v>0.552518</x:v>
+      </x:c>
+      <x:c r="H28" s="43" t="n">
+        <x:v>0.544687</x:v>
+      </x:c>
+      <x:c r="I28" s="42" t="n">
+        <x:f>ABS(H28-0.5)-ABS(C28-0.5)</x:f>
+        <x:v>-0.01325900000000002</x:v>
+      </x:c>
+      <x:c r="J28" s="42" t="n">
+        <x:f>ABS(H28-0.5)-ABS(G28-0.5)</x:f>
+        <x:v>-0.007830999999999921</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="35" customHeight="1">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="34" t="str">
+        <x:v>contract_cred_contract_amt_by_status_nm_wrk_by_product_category_nm_ptb_cc_aggmin</x:v>
+      </x:c>
+      <x:c r="C29" s="42" t="n">
+        <x:v>0.424902</x:v>
+      </x:c>
+      <x:c r="D29" s="42" t="n">
+        <x:v>0.419017</x:v>
+      </x:c>
+      <x:c r="E29" s="42" t="n">
+        <x:v>0.418088</x:v>
+      </x:c>
+      <x:c r="F29" s="42" t="n">
+        <x:v>0.409465</x:v>
+      </x:c>
+      <x:c r="G29" s="42" t="n">
+        <x:v>0.4075</x:v>
+      </x:c>
+      <x:c r="H29" s="42" t="n">
+        <x:v>0.409437</x:v>
+      </x:c>
+      <x:c r="I29" s="42" t="n">
+        <x:f>ABS(H29-0.5)-ABS(C29-0.5)</x:f>
+        <x:v>0.015465000000000007</x:v>
+      </x:c>
+      <x:c r="J29" s="42" t="n">
+        <x:f>ABS(H29-0.5)-ABS(G29-0.5)</x:f>
+        <x:v>-0.001937000000000022</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="35" customHeight="1">
+      <x:c r="A30" s="2"/>
+      <x:c r="B30" s="37" t="str">
+        <x:v>contract_cred_contract_uid_by_status_nm_wrk_aggcnt</x:v>
+      </x:c>
+      <x:c r="C30" s="43" t="n">
+        <x:v>0.734392</x:v>
+      </x:c>
+      <x:c r="D30" s="43" t="n">
+        <x:v>0.702967</x:v>
+      </x:c>
+      <x:c r="E30" s="43" t="n">
+        <x:v>0.668136</x:v>
+      </x:c>
+      <x:c r="F30" s="43" t="n">
+        <x:v>0.645655</x:v>
+      </x:c>
+      <x:c r="G30" s="43" t="n">
+        <x:v>0.632693</x:v>
+      </x:c>
+      <x:c r="H30" s="43" t="n">
+        <x:v>0.616693</x:v>
+      </x:c>
+      <x:c r="I30" s="42" t="n">
+        <x:f>ABS(H30-0.5)-ABS(C30-0.5)</x:f>
+        <x:v>-0.117699</x:v>
+      </x:c>
+      <x:c r="J30" s="42" t="n">
+        <x:f>ABS(H30-0.5)-ABS(G30-0.5)</x:f>
+        <x:v>-0.015999999999999903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="35" customHeight="1">
+      <x:c r="A31" s="2"/>
+      <x:c r="B31" s="34" t="str">
+        <x:v>contract_delinquency_interval_overdue_principal_sum_aggcnt</x:v>
+      </x:c>
+      <x:c r="C31" s="42" t="n">
+        <x:v>0.505943</x:v>
+      </x:c>
+      <x:c r="D31" s="42" t="n">
+        <x:v>0.50381</x:v>
+      </x:c>
+      <x:c r="E31" s="42" t="n">
+        <x:v>0.504546</x:v>
+      </x:c>
+      <x:c r="F31" s="42" t="n">
+        <x:v>0.513567</x:v>
+      </x:c>
+      <x:c r="G31" s="42" t="n">
+        <x:v>0.515418</x:v>
+      </x:c>
+      <x:c r="H31" s="42" t="n">
+        <x:v>0.516555</x:v>
+      </x:c>
+      <x:c r="I31" s="42" t="n">
+        <x:f>ABS(H31-0.5)-ABS(C31-0.5)</x:f>
+        <x:v>0.010611999999999955</x:v>
+      </x:c>
+      <x:c r="J31" s="42" t="n">
+        <x:f>ABS(H31-0.5)-ABS(G31-0.5)</x:f>
+        <x:v>0.0011369999999999436</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="35" customHeight="1">
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="37" t="str">
+        <x:v>contract_delinquency_interval_overdue_principal_sum_aggsum</x:v>
+      </x:c>
+      <x:c r="C32" s="43" t="n">
+        <x:v>0.505729</x:v>
+      </x:c>
+      <x:c r="D32" s="43" t="n">
+        <x:v>0.503575</x:v>
+      </x:c>
+      <x:c r="E32" s="43" t="n">
+        <x:v>0.505258</x:v>
+      </x:c>
+      <x:c r="F32" s="43" t="n">
+        <x:v>0.51344</x:v>
+      </x:c>
+      <x:c r="G32" s="43" t="n">
+        <x:v>0.515302</x:v>
+      </x:c>
+      <x:c r="H32" s="43" t="n">
+        <x:v>0.51149</x:v>
+      </x:c>
+      <x:c r="I32" s="42" t="n">
+        <x:f>ABS(H32-0.5)-ABS(C32-0.5)</x:f>
+        <x:v>0.005761000000000016</x:v>
+      </x:c>
+      <x:c r="J32" s="42" t="n">
+        <x:f>ABS(H32-0.5)-ABS(G32-0.5)</x:f>
+        <x:v>-0.0038120000000000376</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="35" customHeight="1">
+      <x:c r="A33" s="2"/>
+      <x:c r="B33" s="34" t="str">
+        <x:v>contract_agg_monthly_cred_cc_principal_aggmax_3m</x:v>
+      </x:c>
+      <x:c r="C33" s="42" t="n">
+        <x:v>0.601551</x:v>
+      </x:c>
+      <x:c r="D33" s="42" t="n">
+        <x:v>0.599869</x:v>
+      </x:c>
+      <x:c r="E33" s="42" t="n">
+        <x:v>0.602088</x:v>
+      </x:c>
+      <x:c r="F33" s="42" t="n">
+        <x:v>0.605528</x:v>
+      </x:c>
+      <x:c r="G33" s="42" t="n">
+        <x:v>0.603544</x:v>
+      </x:c>
+      <x:c r="H33" s="42" t="n">
+        <x:v>0.599875</x:v>
+      </x:c>
+      <x:c r="I33" s="42" t="n">
+        <x:f>ABS(H33-0.5)-ABS(C33-0.5)</x:f>
+        <x:v>-0.0016759999999998998</x:v>
+      </x:c>
+      <x:c r="J33" s="42" t="n">
+        <x:f>ABS(H33-0.5)-ABS(G33-0.5)</x:f>
+        <x:v>-0.0036689999999999223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="35" customHeight="1">
+      <x:c r="A34" s="2"/>
+      <x:c r="B34" s="37" t="str">
+        <x:v>contract_cred_contract_amt_by_product_category_nm_ptb_cc_aggmax_d90</x:v>
+      </x:c>
+      <x:c r="C34" s="43" t="n">
+        <x:v>0.449016</x:v>
+      </x:c>
+      <x:c r="D34" s="43" t="n">
+        <x:v>0.446532</x:v>
+      </x:c>
+      <x:c r="E34" s="43" t="n">
+        <x:v>0.447038</x:v>
+      </x:c>
+      <x:c r="F34" s="43" t="n">
+        <x:v>0.44235</x:v>
+      </x:c>
+      <x:c r="G34" s="43" t="n">
+        <x:v>0.442998</x:v>
+      </x:c>
+      <x:c r="H34" s="43" t="n">
+        <x:v>0.451008</x:v>
+      </x:c>
+      <x:c r="I34" s="42" t="n">
+        <x:f>ABS(H34-0.5)-ABS(C34-0.5)</x:f>
+        <x:v>-0.0019919999999999938</x:v>
+      </x:c>
+      <x:c r="J34" s="42" t="n">
+        <x:f>ABS(H34-0.5)-ABS(G34-0.5)</x:f>
+        <x:v>-0.008010000000000017</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="35" customHeight="1">
+      <x:c r="A35" s="2"/>
+      <x:c r="B35" s="34" t="str">
+        <x:v>client_birth_diff_death</x:v>
+      </x:c>
+      <x:c r="C35" s="42" t="n">
+        <x:v>0.483224</x:v>
+      </x:c>
+      <x:c r="D35" s="42" t="n">
+        <x:v>0.481583</x:v>
+      </x:c>
+      <x:c r="E35" s="42" t="n">
+        <x:v>0.480307</x:v>
+      </x:c>
+      <x:c r="F35" s="42" t="n">
+        <x:v>0.476977</x:v>
+      </x:c>
+      <x:c r="G35" s="42" t="n">
+        <x:v>0.474726</x:v>
+      </x:c>
+      <x:c r="H35" s="42" t="n">
+        <x:v>0.476541</x:v>
+      </x:c>
+      <x:c r="I35" s="42" t="n">
+        <x:f>ABS(H35-0.5)-ABS(C35-0.5)</x:f>
+        <x:v>0.0066829999999999945</x:v>
+      </x:c>
+      <x:c r="J35" s="42" t="n">
+        <x:f>ABS(H35-0.5)-ABS(G35-0.5)</x:f>
+        <x:v>-0.001815000000000011</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="35" customHeight="1">
+      <x:c r="A36" s="2"/>
+      <x:c r="B36" s="37" t="str">
+        <x:v>contract_cred_current_debt_amt_by_status_nm_wrk_aggsum</x:v>
+      </x:c>
+      <x:c r="C36" s="43" t="n">
+        <x:v>0.691702</x:v>
+      </x:c>
+      <x:c r="D36" s="43" t="n">
+        <x:v>0.661424</x:v>
+      </x:c>
+      <x:c r="E36" s="43" t="n">
+        <x:v>0.635187</x:v>
+      </x:c>
+      <x:c r="F36" s="43" t="n">
+        <x:v>0.619509</x:v>
+      </x:c>
+      <x:c r="G36" s="43" t="n">
+        <x:v>0.612176</x:v>
+      </x:c>
+      <x:c r="H36" s="43" t="n">
+        <x:v>0.603001</x:v>
+      </x:c>
+      <x:c r="I36" s="42" t="n">
+        <x:f>ABS(H36-0.5)-ABS(C36-0.5)</x:f>
+        <x:v>-0.08870100000000003</x:v>
+      </x:c>
+      <x:c r="J36" s="42" t="n">
+        <x:f>ABS(H36-0.5)-ABS(G36-0.5)</x:f>
+        <x:v>-0.009175000000000044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="35" customHeight="1">
+      <x:c r="A37" s="2"/>
+      <x:c r="B37" s="34" t="str">
+        <x:v>contract_agg_monthly_cred_cntr_current_principal_sum_ratio_last_avg_3m</x:v>
+      </x:c>
+      <x:c r="C37" s="42" t="n">
+        <x:v>0.524673</x:v>
+      </x:c>
+      <x:c r="D37" s="42" t="n">
+        <x:v>0.526907</x:v>
+      </x:c>
+      <x:c r="E37" s="42" t="n">
+        <x:v>0.529438</x:v>
+      </x:c>
+      <x:c r="F37" s="42" t="n">
+        <x:v>0.524389</x:v>
+      </x:c>
+      <x:c r="G37" s="42" t="n">
+        <x:v>0.520298</x:v>
+      </x:c>
+      <x:c r="H37" s="42" t="n">
+        <x:v>0.510066</x:v>
+      </x:c>
+      <x:c r="I37" s="42" t="n">
+        <x:f>ABS(H37-0.5)-ABS(C37-0.5)</x:f>
+        <x:v>-0.014606999999999926</x:v>
+      </x:c>
+      <x:c r="J37" s="42" t="n">
+        <x:f>ABS(H37-0.5)-ABS(G37-0.5)</x:f>
+        <x:v>-0.010232000000000019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="35" customHeight="1">
+      <x:c r="A38" s="2"/>
+      <x:c r="B38" s="37" t="str">
+        <x:v>current_debt</x:v>
+      </x:c>
+      <x:c r="C38" s="43" t="n">
+        <x:v>0.61083</x:v>
+      </x:c>
+      <x:c r="D38" s="43" t="n">
+        <x:v>0.608911</x:v>
+      </x:c>
+      <x:c r="E38" s="43" t="n">
+        <x:v>0.609659</x:v>
+      </x:c>
+      <x:c r="F38" s="43" t="n">
+        <x:v>0.609354</x:v>
+      </x:c>
+      <x:c r="G38" s="43" t="n">
+        <x:v>0.608104</x:v>
+      </x:c>
+      <x:c r="H38" s="43" t="n">
+        <x:v>0.603682</x:v>
+      </x:c>
+      <x:c r="I38" s="42" t="n">
+        <x:f>ABS(H38-0.5)-ABS(C38-0.5)</x:f>
+        <x:v>-0.007147999999999932</x:v>
+      </x:c>
+      <x:c r="J38" s="42" t="n">
+        <x:f>ABS(H38-0.5)-ABS(G38-0.5)</x:f>
+        <x:v>-0.004421999999999926</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="35" customHeight="1">
+      <x:c r="A39" s="2"/>
+      <x:c r="B39" s="34" t="str">
+        <x:v>contract_cred_current_debt_amt_by_status_nm_wrk_aggavg</x:v>
+      </x:c>
+      <x:c r="C39" s="42" t="n">
+        <x:v>0.593912</x:v>
+      </x:c>
+      <x:c r="D39" s="42" t="n">
+        <x:v>0.583537</x:v>
+      </x:c>
+      <x:c r="E39" s="42" t="n">
+        <x:v>0.577145</x:v>
+      </x:c>
+      <x:c r="F39" s="42" t="n">
+        <x:v>0.571336</x:v>
+      </x:c>
+      <x:c r="G39" s="42" t="n">
+        <x:v>0.567182</x:v>
+      </x:c>
+      <x:c r="H39" s="42" t="n">
+        <x:v>0.562445</x:v>
+      </x:c>
+      <x:c r="I39" s="42" t="n">
+        <x:f>ABS(H39-0.5)-ABS(C39-0.5)</x:f>
+        <x:v>-0.03146700000000002</x:v>
+      </x:c>
+      <x:c r="J39" s="42" t="n">
+        <x:f>ABS(H39-0.5)-ABS(G39-0.5)</x:f>
+        <x:v>-0.004736999999999991</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="35" customHeight="1">
+      <x:c r="A40" s="2"/>
+      <x:c r="B40" s="37" t="str">
+        <x:v>card_card_uid_by_status_card_nm_aggcnt</x:v>
+      </x:c>
+      <x:c r="C40" s="43" t="n">
+        <x:v>0.533167</x:v>
+      </x:c>
+      <x:c r="D40" s="43" t="n">
+        <x:v>0.53276</x:v>
+      </x:c>
+      <x:c r="E40" s="43" t="n">
+        <x:v>0.533093</x:v>
+      </x:c>
+      <x:c r="F40" s="43" t="n">
+        <x:v>0.534945</x:v>
+      </x:c>
+      <x:c r="G40" s="43" t="n">
+        <x:v>0.535634</x:v>
+      </x:c>
+      <x:c r="H40" s="43" t="n">
+        <x:v>0.528337</x:v>
+      </x:c>
+      <x:c r="I40" s="42" t="n">
+        <x:f>ABS(H40-0.5)-ABS(C40-0.5)</x:f>
+        <x:v>-0.004830000000000001</x:v>
+      </x:c>
+      <x:c r="J40" s="42" t="n">
+        <x:f>ABS(H40-0.5)-ABS(G40-0.5)</x:f>
+        <x:v>-0.007297000000000109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="35" customHeight="1">
+      <x:c r="A41" s="2"/>
+      <x:c r="B41" s="34" t="str">
+        <x:v>contract_delinquency_interval_contract_uid_aggcnt_d180</x:v>
+      </x:c>
+      <x:c r="C41" s="42" t="n">
+        <x:v>0.534038</x:v>
+      </x:c>
+      <x:c r="D41" s="42" t="n">
+        <x:v>0.539278</x:v>
+      </x:c>
+      <x:c r="E41" s="42" t="n">
+        <x:v>0.549621</x:v>
+      </x:c>
+      <x:c r="F41" s="42" t="n">
+        <x:v>0.574759</x:v>
+      </x:c>
+      <x:c r="G41" s="42" t="n">
+        <x:v>0.575224</x:v>
+      </x:c>
+      <x:c r="H41" s="42" t="n">
+        <x:v>0.561847</x:v>
+      </x:c>
+      <x:c r="I41" s="42" t="n">
+        <x:f>ABS(H41-0.5)-ABS(C41-0.5)</x:f>
+        <x:v>0.027808999999999973</x:v>
+      </x:c>
+      <x:c r="J41" s="42" t="n">
+        <x:f>ABS(H41-0.5)-ABS(G41-0.5)</x:f>
+        <x:v>-0.013376999999999972</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="35" customHeight="1">
+      <x:c r="A42" s="2"/>
+      <x:c r="B42" s="37" t="str">
+        <x:v>contract_agg_monthly_cred_cc_utilized_limit_aggavg_3m</x:v>
+      </x:c>
+      <x:c r="C42" s="43" t="n">
+        <x:v>0.626347</x:v>
+      </x:c>
+      <x:c r="D42" s="43" t="n">
+        <x:v>0.624828</x:v>
+      </x:c>
+      <x:c r="E42" s="43" t="n">
+        <x:v>0.627302</x:v>
+      </x:c>
+      <x:c r="F42" s="43" t="n">
+        <x:v>0.632932</x:v>
+      </x:c>
+      <x:c r="G42" s="43" t="n">
+        <x:v>0.630943</x:v>
+      </x:c>
+      <x:c r="H42" s="43" t="n">
+        <x:v>0.62459</x:v>
+      </x:c>
+      <x:c r="I42" s="42" t="n">
+        <x:f>ABS(H42-0.5)-ABS(C42-0.5)</x:f>
+        <x:v>-0.0017570000000000086</x:v>
+      </x:c>
+      <x:c r="J42" s="42" t="n">
+        <x:f>ABS(H42-0.5)-ABS(G42-0.5)</x:f>
+        <x:v>-0.006353000000000053</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="35" customHeight="1">
+      <x:c r="A43" s="2"/>
+      <x:c r="B43" s="34" t="str">
+        <x:v>contract_agg_monthly_cred_cc_debt_aggmax_3m</x:v>
+      </x:c>
+      <x:c r="C43" s="42" t="n">
+        <x:v>0.606819</x:v>
+      </x:c>
+      <x:c r="D43" s="42" t="n">
+        <x:v>0.605616</x:v>
+      </x:c>
+      <x:c r="E43" s="42" t="n">
+        <x:v>0.608006</x:v>
+      </x:c>
+      <x:c r="F43" s="42" t="n">
+        <x:v>0.612318</x:v>
+      </x:c>
+      <x:c r="G43" s="42" t="n">
+        <x:v>0.609925</x:v>
+      </x:c>
+      <x:c r="H43" s="42" t="n">
+        <x:v>0.6052</x:v>
+      </x:c>
+      <x:c r="I43" s="42" t="n">
+        <x:f>ABS(H43-0.5)-ABS(C43-0.5)</x:f>
+        <x:v>-0.001619000000000037</x:v>
+      </x:c>
+      <x:c r="J43" s="42" t="n">
+        <x:f>ABS(H43-0.5)-ABS(G43-0.5)</x:f>
+        <x:v>-0.00472500000000009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="35" customHeight="1">
+      <x:c r="A44" s="2"/>
+      <x:c r="B44" s="37" t="str">
+        <x:v>contract_agg_monthly_cred_cntr_grace_flag_months_since_last_pos</x:v>
+      </x:c>
+      <x:c r="C44" s="43" t="n">
+        <x:v>0.487618</x:v>
+      </x:c>
+      <x:c r="D44" s="43" t="n">
+        <x:v>0.608</x:v>
+      </x:c>
+      <x:c r="E44" s="43" t="n">
+        <x:v>0.622466</x:v>
+      </x:c>
+      <x:c r="F44" s="43" t="n">
+        <x:v>0.637867</x:v>
+      </x:c>
+      <x:c r="G44" s="43" t="n">
+        <x:v>0.640747</x:v>
+      </x:c>
+      <x:c r="H44" s="43" t="n">
+        <x:v>0.63146</x:v>
+      </x:c>
+      <x:c r="I44" s="42" t="n">
+        <x:f>ABS(H44-0.5)-ABS(C44-0.5)</x:f>
+        <x:v>0.11907800000000002</x:v>
+      </x:c>
+      <x:c r="J44" s="42" t="n">
+        <x:f>ABS(H44-0.5)-ABS(G44-0.5)</x:f>
+        <x:v>-0.009286999999999934</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="35" customHeight="1">
+      <x:c r="A45" s="2"/>
+      <x:c r="B45" s="34" t="str">
+        <x:v>contract_agg_monthly_cred_cc_debt_aggsum_1m</x:v>
+      </x:c>
+      <x:c r="C45" s="42" t="n">
+        <x:v>0.629344</x:v>
+      </x:c>
+      <x:c r="D45" s="42" t="n">
+        <x:v>0.629416</x:v>
+      </x:c>
+      <x:c r="E45" s="42" t="n">
+        <x:v>0.631857</x:v>
+      </x:c>
+      <x:c r="F45" s="42" t="n">
+        <x:v>0.637113</x:v>
+      </x:c>
+      <x:c r="G45" s="42" t="n">
+        <x:v>0.634485</x:v>
+      </x:c>
+      <x:c r="H45" s="42" t="n">
+        <x:v>0.62726</x:v>
+      </x:c>
+      <x:c r="I45" s="42" t="n">
+        <x:f>ABS(H45-0.5)-ABS(C45-0.5)</x:f>
+        <x:v>-0.0020839999999999748</x:v>
+      </x:c>
+      <x:c r="J45" s="42" t="n">
+        <x:f>ABS(H45-0.5)-ABS(G45-0.5)</x:f>
+        <x:v>-0.007224999999999926</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="35" customHeight="1">
+      <x:c r="A46" s="2"/>
+      <x:c r="B46" s="37" t="str">
+        <x:v>contract_agg_monthly_cred_cntr_current_debit_client_turn_sum_1m</x:v>
+      </x:c>
+      <x:c r="C46" s="43" t="n">
+        <x:v>0.5056</x:v>
+      </x:c>
+      <x:c r="D46" s="43" t="n">
+        <x:v>0.508012</x:v>
+      </x:c>
+      <x:c r="E46" s="43" t="n">
+        <x:v>0.504392</x:v>
+      </x:c>
+      <x:c r="F46" s="43" t="n">
+        <x:v>0.496333</x:v>
+      </x:c>
+      <x:c r="G46" s="43" t="n">
+        <x:v>0.485322</x:v>
+      </x:c>
+      <x:c r="H46" s="43" t="n">
+        <x:v>0.497521</x:v>
+      </x:c>
+      <x:c r="I46" s="42" t="n">
+        <x:f>ABS(H46-0.5)-ABS(C46-0.5)</x:f>
+        <x:v>-0.0031210000000000404</x:v>
+      </x:c>
+      <x:c r="J46" s="42" t="n">
+        <x:f>ABS(H46-0.5)-ABS(G46-0.5)</x:f>
+        <x:v>-0.012199000000000015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="35" customHeight="1">
+      <x:c r="A47" s="2"/>
+      <x:c r="B47" s="34" t="str">
+        <x:v>contract_agg_monthly_cred_cc_principal_aggsum_1m</x:v>
+      </x:c>
+      <x:c r="C47" s="42" t="n">
+        <x:v>0.625544</x:v>
+      </x:c>
+      <x:c r="D47" s="42" t="n">
+        <x:v>0.625989</x:v>
+      </x:c>
+      <x:c r="E47" s="42" t="n">
+        <x:v>0.628741</x:v>
+      </x:c>
+      <x:c r="F47" s="42" t="n">
+        <x:v>0.632929</x:v>
+      </x:c>
+      <x:c r="G47" s="42" t="n">
+        <x:v>0.630489</x:v>
+      </x:c>
+      <x:c r="H47" s="42" t="n">
+        <x:v>0.621783</x:v>
+      </x:c>
+      <x:c r="I47" s="42" t="n">
+        <x:f>ABS(H47-0.5)-ABS(C47-0.5)</x:f>
+        <x:v>-0.0037610000000000143</x:v>
+      </x:c>
+      <x:c r="J47" s="42" t="n">
+        <x:f>ABS(H47-0.5)-ABS(G47-0.5)</x:f>
+        <x:v>-0.008705999999999992</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="35" customHeight="1">
+      <x:c r="A48" s="2"/>
+      <x:c r="B48" s="37" t="str">
+        <x:v>contract_agg_monthly_cred_cc_debt_aggavg_3m</x:v>
+      </x:c>
+      <x:c r="C48" s="43" t="n">
+        <x:v>0.629034</x:v>
+      </x:c>
+      <x:c r="D48" s="43" t="n">
+        <x:v>0.627936</x:v>
+      </x:c>
+      <x:c r="E48" s="43" t="n">
+        <x:v>0.631121</x:v>
+      </x:c>
+      <x:c r="F48" s="43" t="n">
+        <x:v>0.636978</x:v>
+      </x:c>
+      <x:c r="G48" s="43" t="n">
+        <x:v>0.634984</x:v>
+      </x:c>
+      <x:c r="H48" s="43" t="n">
+        <x:v>0.628926</x:v>
+      </x:c>
+      <x:c r="I48" s="42" t="n">
+        <x:f>ABS(H48-0.5)-ABS(C48-0.5)</x:f>
+        <x:v>-0.00010799999999999699</x:v>
+      </x:c>
+      <x:c r="J48" s="42" t="n">
+        <x:f>ABS(H48-0.5)-ABS(G48-0.5)</x:f>
+        <x:v>-0.006058000000000008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="35" customHeight="1">
+      <x:c r="A49" s="2"/>
+      <x:c r="B49" s="34" t="str">
+        <x:v>contract_agg_monthly_cred_cc_principal_aggavg_3m</x:v>
+      </x:c>
+      <x:c r="C49" s="42" t="n">
+        <x:v>0.624744</x:v>
+      </x:c>
+      <x:c r="D49" s="42" t="n">
+        <x:v>0.623687</x:v>
+      </x:c>
+      <x:c r="E49" s="42" t="n">
+        <x:v>0.626917</x:v>
+      </x:c>
+      <x:c r="F49" s="42" t="n">
+        <x:v>0.632337</x:v>
+      </x:c>
+      <x:c r="G49" s="42" t="n">
+        <x:v>0.630637</x:v>
+      </x:c>
+      <x:c r="H49" s="42" t="n">
+        <x:v>0.623602</x:v>
+      </x:c>
+      <x:c r="I49" s="42" t="n">
+        <x:f>ABS(H49-0.5)-ABS(C49-0.5)</x:f>
+        <x:v>-0.0011419999999999764</x:v>
+      </x:c>
+      <x:c r="J49" s="42" t="n">
+        <x:f>ABS(H49-0.5)-ABS(G49-0.5)</x:f>
+        <x:v>-0.0070350000000000135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="23" customHeight="1">
+      <x:c r="A50" s="2"/>
+      <x:c r="B50" s="2"/>
+      <x:c r="C50" s="2"/>
+      <x:c r="D50" s="2"/>
+      <x:c r="E50" s="2"/>
+      <x:c r="F50" s="2"/>
+      <x:c r="G50" s="2"/>
+      <x:c r="H50" s="1"/>
+      <x:c r="I50" s="1"/>
+      <x:c r="J50" s="1"/>
+    </x:row>
+    <x:row r="51" ht="23" customHeight="1">
+      <x:c r="A51" s="2"/>
+      <x:c r="B51" s="4" t="str">
+        <x:v>Категориальный признак sf_loanstype_offline_currentdelq_3yopen_aggmax в числовой AUC не включён.</x:v>
+      </x:c>
+      <x:c r="C51" s="2"/>
+      <x:c r="D51" s="2"/>
+      <x:c r="E51" s="2"/>
+      <x:c r="F51" s="2"/>
+      <x:c r="G51" s="2"/>
+      <x:c r="H51" s="1"/>
+      <x:c r="I51" s="1"/>
+      <x:c r="J51" s="1"/>
+    </x:row>
+    <x:row r="52" ht="23" customHeight="1">
+      <x:c r="A52" s="2"/>
+      <x:c r="B52" s="4" t="str">
+        <x:v>Связь категориального признака с таргетом проверялась через долю Y=1 и численность по категориям в monthly_feature_bins.</x:v>
+      </x:c>
+      <x:c r="C52" s="2"/>
+      <x:c r="D52" s="2"/>
+      <x:c r="E52" s="2"/>
+      <x:c r="F52" s="2"/>
+      <x:c r="G52" s="2"/>
+      <x:c r="H52" s="1"/>
+      <x:c r="I52" s="1"/>
+      <x:c r="J52" s="1"/>
+    </x:row>
+    <x:row r="53" ht="23" customHeight="1">
+      <x:c r="A53" s="2"/>
+      <x:c r="B53" s="4" t="str">
+        <x:v>Численности и доли пропусков для каждого признака и месяца доступны в исходном DataFrame monthly_feature_auc.</x:v>
+      </x:c>
+      <x:c r="C53" s="2"/>
+      <x:c r="D53" s="2"/>
+      <x:c r="E53" s="2"/>
+      <x:c r="F53" s="2"/>
+      <x:c r="G53" s="2"/>
+      <x:c r="H53" s="1"/>
+      <x:c r="I53" s="1"/>
+      <x:c r="J53" s="1"/>
+    </x:row>
+    <x:row r="54" ht="23" customHeight="1">
+      <x:c r="A54" s="2"/>
+      <x:c r="B54" s="2"/>
+      <x:c r="C54" s="2"/>
+      <x:c r="D54" s="2"/>
+      <x:c r="E54" s="2"/>
+      <x:c r="F54" s="2"/>
+      <x:c r="G54" s="2"/>
+      <x:c r="H54" s="1"/>
+      <x:c r="I54" s="1"/>
+      <x:c r="J54" s="1"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF6E829F"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="65" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="62" hidden="0" customWidth="1"/>
@@ -2899,16 +4396,16 @@
     </x:row>
     <x:row r="6" ht="85" customHeight="1">
       <x:c r="A6" s="2"/>
-      <x:c r="B6" s="42" t="str">
+      <x:c r="B6" s="44" t="str">
         <x:v>ROC-AUC модели</x:v>
       </x:c>
-      <x:c r="C6" s="42" t="str">
+      <x:c r="C6" s="44" t="str">
         <x:v>roc_auc_score(Y, predict_proba(X)[:,1]); отдельно по месяцам. Сентябрь–декабрь: OOS.</x:v>
       </x:c>
-      <x:c r="D6" s="42" t="str">
+      <x:c r="D6" s="44" t="str">
         <x:v>Ранжирование без порога классификации. Доля таргета и n_eval подписаны отдельно.</x:v>
       </x:c>
-      <x:c r="E6" s="42" t="str">
+      <x:c r="E6" s="44" t="str">
         <x:v>Результаты есть</x:v>
       </x:c>
       <x:c r="F6" s="2"/>
@@ -2916,16 +4413,16 @@
     </x:row>
     <x:row r="7" ht="85" customHeight="1">
       <x:c r="A7" s="2"/>
-      <x:c r="B7" s="43" t="str">
+      <x:c r="B7" s="45" t="str">
         <x:v>Состав контрактов</x:v>
       </x:c>
-      <x:c r="C7" s="43" t="str">
+      <x:c r="C7" s="45" t="str">
         <x:v>Сопоставление по contract_uid в паре месяцев. Непрерывные величины присоединены по contract_uid + report_date.</x:v>
       </x:c>
-      <x:c r="D7" s="43" t="str">
+      <x:c r="D7" s="45" t="str">
         <x:v>220 563 общих контракта января–февраля; сохраняется падение AUC.</x:v>
       </x:c>
-      <x:c r="E7" s="43" t="str">
+      <x:c r="E7" s="45" t="str">
         <x:v>Результаты есть</x:v>
       </x:c>
       <x:c r="F7" s="2"/>
@@ -2933,16 +4430,16 @@
     </x:row>
     <x:row r="8" ht="85" customHeight="1">
       <x:c r="A8" s="2"/>
-      <x:c r="B8" s="42" t="str">
+      <x:c r="B8" s="44" t="str">
         <x:v>Однофакторный AUC</x:v>
       </x:c>
-      <x:c r="C8" s="42" t="str">
+      <x:c r="C8" s="44" t="str">
         <x:v>Числовой признак как скор; конечные заполненные значения. Полная база и общие контракты отдельно.</x:v>
       </x:c>
-      <x:c r="D8" s="42" t="str">
+      <x:c r="D8" s="44" t="str">
         <x:v>Сила = |AUC−0,5|. Не отражает все нелинейные связи и взаимодействия.</x:v>
       </x:c>
-      <x:c r="E8" s="42" t="str">
+      <x:c r="E8" s="44" t="str">
         <x:v>Результаты есть</x:v>
       </x:c>
       <x:c r="F8" s="2"/>
@@ -2950,16 +4447,16 @@
     </x:row>
     <x:row r="9" ht="85" customHeight="1">
       <x:c r="A9" s="2"/>
-      <x:c r="B9" s="43" t="str">
+      <x:c r="B9" s="45" t="str">
         <x:v>Фиксированные интервалы</x:v>
       </x:c>
-      <x:c r="C9" s="43" t="str">
+      <x:c r="C9" s="45" t="str">
         <x:v>Квантили сентября 20/40/60/80%; одинаковые границы всех месяцев. Отдельно пропуски, категории и число строк.</x:v>
       </x:c>
-      <x:c r="D9" s="43" t="str">
+      <x:c r="D9" s="45" t="str">
         <x:v>Доля Y=1 при сопоставимых значениях признака. Ранние январь–февральские таблицы имели январские границы.</x:v>
       </x:c>
-      <x:c r="E9" s="43" t="str">
+      <x:c r="E9" s="45" t="str">
         <x:v>Результаты есть</x:v>
       </x:c>
       <x:c r="F9" s="2"/>
@@ -2967,16 +4464,16 @@
     </x:row>
     <x:row r="10" ht="85" customHeight="1">
       <x:c r="A10" s="2"/>
-      <x:c r="B10" s="42" t="str">
+      <x:c r="B10" s="44" t="str">
         <x:v>PSI признаков</x:v>
       </x:c>
-      <x:c r="C10" s="42" t="str">
+      <x:c r="C10" s="44" t="str">
         <x:v>Все 40 признаков. Каждый месяц сравнивается с сентябрём 2025. По коду отбор при max PSI≥0,15 либо положительном тренде, p&lt;0,05 и max PSI&gt;0,10.</x:v>
       </x:c>
-      <x:c r="D10" s="42" t="str">
+      <x:c r="D10" s="44" t="str">
         <x:v>Февраль: все 40 PSI&lt;0,10, максимум 0,0602532. За весь период максимум 0,1074575. Низкий PSI не гарантирует устойчивость связи с Y.</x:v>
       </x:c>
-      <x:c r="E10" s="42" t="str">
+      <x:c r="E10" s="44" t="str">
         <x:v>Значения получены</x:v>
       </x:c>
       <x:c r="F10" s="2"/>
@@ -2984,16 +4481,16 @@
     </x:row>
     <x:row r="11" ht="85" customHeight="1">
       <x:c r="A11" s="2"/>
-      <x:c r="B11" s="43" t="str">
+      <x:c r="B11" s="45" t="str">
         <x:v>Переходы таргета</x:v>
       </x:c>
-      <x:c r="C11" s="43" t="str">
+      <x:c r="C11" s="45" t="str">
         <x:v>Четыре перехода на общих контрактах соседних месяцев. Частота 1→0 среди исходных единиц; 0→1 среди исходных нулей.</x:v>
       </x:c>
-      <x:c r="D11" s="43" t="str">
+      <x:c r="D11" s="45" t="str">
         <x:v>Рост смен метки до 5,50%. Нельзя сравнивать частоты с разными знаменателями.</x:v>
       </x:c>
-      <x:c r="E11" s="43" t="str">
+      <x:c r="E11" s="45" t="str">
         <x:v>Результаты есть</x:v>
       </x:c>
       <x:c r="F11" s="2"/>
@@ -3001,16 +4498,16 @@
     </x:row>
     <x:row r="12" ht="85" customHeight="1">
       <x:c r="A12" s="2"/>
-      <x:c r="B12" s="42" t="str">
+      <x:c r="B12" s="44" t="str">
         <x:v>Четыре сравнения AUC</x:v>
       </x:c>
-      <x:c r="C12" s="42" t="str">
+      <x:c r="C12" s="44" t="str">
         <x:v>Каждый вид единиц против каждого вида нулей. Вес AUC = доля соответствующих пар единица–ноль.</x:v>
       </x:c>
-      <x:c r="D12" s="42" t="str">
+      <x:c r="D12" s="44" t="str">
         <x:v>Устойчивые исходы тоже разделяются хуже. Между месячными сравнениями меняется состав общих контрактов.</x:v>
       </x:c>
-      <x:c r="E12" s="42" t="str">
+      <x:c r="E12" s="44" t="str">
         <x:v>Результаты есть</x:v>
       </x:c>
       <x:c r="F12" s="2"/>
@@ -3018,16 +4515,16 @@
     </x:row>
     <x:row r="13" ht="85" customHeight="1">
       <x:c r="A13" s="2"/>
-      <x:c r="B13" s="43" t="str">
+      <x:c r="B13" s="45" t="str">
         <x:v>Долг и лимит</x:v>
       </x:c>
-      <x:c r="C13" s="43" t="str">
+      <x:c r="C13" s="45" t="str">
         <x:v>Для переходов 1→0 пересчитано отношение нового будущего долга к прежнему лимиту.</x:v>
       </x:c>
-      <x:c r="D13" s="43" t="str">
+      <x:c r="D13" s="45" t="str">
         <x:v>У 95,34% переход сохраняется при прежнем лимите. Проверка механики таргета, без оценки вклада в падение AUC.</x:v>
       </x:c>
-      <x:c r="E13" s="43" t="str">
+      <x:c r="E13" s="45" t="str">
         <x:v>Результаты есть</x:v>
       </x:c>
       <x:c r="F13" s="2"/>
@@ -3035,16 +4532,16 @@
     </x:row>
     <x:row r="14" ht="85" customHeight="1">
       <x:c r="A14" s="2"/>
-      <x:c r="B14" s="42" t="str">
+      <x:c r="B14" s="44" t="str">
         <x:v>Возраст и дата клипа</x:v>
       </x:c>
-      <x:c r="C14" s="42" t="str">
+      <x:c r="C14" s="44" t="str">
         <x:v>Разности календарных дат; для переходов берётся первая дата пары. Сравнение частот и AUC по диапазонам.</x:v>
       </x:c>
-      <x:c r="D14" s="42" t="str">
+      <x:c r="D14" s="44" t="str">
         <x:v>Ухудшение во всех диапазонах. 32–34% клипов без даты; 7,7–8,6% дат раньше открытия — смысл нужно уточнить.</x:v>
       </x:c>
-      <x:c r="E14" s="42" t="str">
+      <x:c r="E14" s="44" t="str">
         <x:v>Результаты есть</x:v>
       </x:c>
       <x:c r="F14" s="2"/>
@@ -3052,16 +4549,16 @@
     </x:row>
     <x:row r="15" ht="85" customHeight="1">
       <x:c r="A15" s="2"/>
-      <x:c r="B15" s="43" t="str">
+      <x:c r="B15" s="45" t="str">
         <x:v>Варианты обучения</x:v>
       </x:c>
-      <x:c r="C15" s="43" t="str">
+      <x:c r="C15" s="45" t="str">
         <x:v>Сентябрь–декабрь; ноябрь–декабрь; декабрь; одна строка на контракт; исключение 10/13 признаков.</x:v>
       </x:c>
-      <x:c r="D15" s="43" t="str">
+      <x:c r="D15" s="45" t="str">
         <x:v>Общие внешние месяцы. Параметры унаследованы; нет доверительных интервалов и полного нового подбора.</x:v>
       </x:c>
-      <x:c r="E15" s="43" t="str">
+      <x:c r="E15" s="45" t="str">
         <x:v>Результаты есть</x:v>
       </x:c>
       <x:c r="F15" s="2"/>
@@ -3069,16 +4566,16 @@
     </x:row>
     <x:row r="16" ht="85" customHeight="1">
       <x:c r="A16" s="2"/>
-      <x:c r="B16" s="42" t="str">
+      <x:c r="B16" s="44" t="str">
         <x:v>Полезность в модели</x:v>
       </x:c>
-      <x:c r="C16" s="42" t="str">
+      <x:c r="C16" s="44" t="str">
         <x:v>Предложено: помесячное изменение AUC при перестановке важных признаков и связанных групп.</x:v>
       </x:c>
-      <x:c r="D16" s="42" t="str">
+      <x:c r="D16" s="44" t="str">
         <x:v>Дополняет gain и однофакторный AUC. Коррелирующие признаки требуют совместной проверки.</x:v>
       </x:c>
-      <x:c r="E16" s="42" t="str">
+      <x:c r="E16" s="44" t="str">
         <x:v>Следующий шаг</x:v>
       </x:c>
       <x:c r="F16" s="2"/>
@@ -3086,16 +4583,16 @@
     </x:row>
     <x:row r="17" ht="85" customHeight="1">
       <x:c r="A17" s="2"/>
-      <x:c r="B17" s="43" t="str">
+      <x:c r="B17" s="45" t="str">
         <x:v>Лимит в признаках</x:v>
       </x:c>
-      <x:c r="C17" s="43" t="str">
+      <x:c r="C17" s="45" t="str">
         <x:v>Предложено: абсолютный долг, лимит, utilization и их прошлые изменения; сравнение при изменении лимита.</x:v>
       </x:c>
-      <x:c r="D17" s="43" t="str">
+      <x:c r="D17" s="45" t="str">
         <x:v>Позволит выделить общий знаменатель и отличить его механику от изменения задолженности.</x:v>
       </x:c>
-      <x:c r="E17" s="43" t="str">
+      <x:c r="E17" s="45" t="str">
         <x:v>Следующий шаг</x:v>
       </x:c>
       <x:c r="F17" s="2"/>
@@ -3103,16 +4600,16 @@
     </x:row>
     <x:row r="18" ht="85" customHeight="1">
       <x:c r="A18" s="2"/>
-      <x:c r="B18" s="42" t="str">
+      <x:c r="B18" s="44" t="str">
         <x:v>Историческая динамика</x:v>
       </x:c>
-      <x:c r="C18" s="42" t="str">
+      <x:c r="C18" s="44" t="str">
         <x:v>Предложено: изменения до report_date за 30/90 дней, тренды долга и utilization, активность и погашения.</x:v>
       </x:c>
-      <x:c r="D18" s="42" t="str">
+      <x:c r="D18" s="44" t="str">
         <x:v>Использовать только доступную на дату историю. Соседние случайные месячные даты не всегда отстоят на 30 дней.</x:v>
       </x:c>
-      <x:c r="E18" s="42" t="str">
+      <x:c r="E18" s="44" t="str">
         <x:v>Следующий шаг</x:v>
       </x:c>
       <x:c r="F18" s="2"/>
@@ -3129,7 +4626,7 @@
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
       <x:c r="A20" s="2"/>
-      <x:c r="B20" s="44" t="str">
+      <x:c r="B20" s="46" t="str">
         <x:v>Ограничения оценки</x:v>
       </x:c>
       <x:c r="C20" s="2"/>
